--- a/Supplier_Intelligence_Report_2025_v3.xlsx
+++ b/Supplier_Intelligence_Report_2025_v3.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2364" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2364" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,9 @@
     <sheet name="Quality Analysis" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Top 20 Performers" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplier Rankings'!$B$1:$B$578</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -3536,6 +3539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K578"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3585,7 +3589,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3620,7 +3624,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -3655,7 +3659,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -3690,7 +3694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -3725,7 +3729,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -3760,7 +3764,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -3795,7 +3799,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -3830,7 +3834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -3865,7 +3869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -3900,7 +3904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -3935,7 +3939,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -3970,7 +3974,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -4005,7 +4009,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -4040,7 +4044,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -4075,7 +4079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -4110,7 +4114,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -4145,7 +4149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -4215,7 +4219,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -4250,7 +4254,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -4285,7 +4289,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -4320,7 +4324,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -4355,7 +4359,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -4390,7 +4394,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -4425,7 +4429,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -4460,7 +4464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -4495,7 +4499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -4530,7 +4534,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -4565,7 +4569,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -4600,7 +4604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -4635,7 +4639,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -4670,7 +4674,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -4705,7 +4709,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -4740,7 +4744,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -4775,7 +4779,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -4810,7 +4814,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -4845,7 +4849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -4880,7 +4884,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -4915,7 +4919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -4950,7 +4954,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -4985,7 +4989,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -5020,7 +5024,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -5055,7 +5059,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -5090,7 +5094,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -5125,7 +5129,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -5160,7 +5164,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -5195,7 +5199,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -5230,7 +5234,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -5265,7 +5269,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -5300,7 +5304,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -5335,7 +5339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -5370,7 +5374,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -5405,7 +5409,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -5440,7 +5444,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -5475,7 +5479,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -5510,7 +5514,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -5545,7 +5549,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -5580,7 +5584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -5615,7 +5619,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -5650,7 +5654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -5685,7 +5689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -5720,7 +5724,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -5790,7 +5794,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -5825,7 +5829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -5860,7 +5864,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -5895,7 +5899,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -5930,7 +5934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -5965,7 +5969,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -6000,7 +6004,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>70</v>
       </c>
@@ -6035,7 +6039,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -6070,7 +6074,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -6105,7 +6109,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -6140,7 +6144,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -6175,7 +6179,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>75</v>
       </c>
@@ -6210,7 +6214,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -6245,7 +6249,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -6280,7 +6284,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -6315,7 +6319,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>79</v>
       </c>
@@ -6350,7 +6354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -6385,7 +6389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>81</v>
       </c>
@@ -6420,7 +6424,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>82</v>
       </c>
@@ -6455,7 +6459,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
         <v>83</v>
       </c>
@@ -6490,7 +6494,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
         <v>84</v>
       </c>
@@ -6525,7 +6529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>85</v>
       </c>
@@ -6560,7 +6564,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -6595,7 +6599,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -6630,7 +6634,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -6665,7 +6669,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>89</v>
       </c>
@@ -6700,7 +6704,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -6735,7 +6739,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -6770,7 +6774,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>92</v>
       </c>
@@ -6805,7 +6809,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
         <v>93</v>
       </c>
@@ -6840,7 +6844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>94</v>
       </c>
@@ -6875,7 +6879,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -6910,7 +6914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
         <v>96</v>
       </c>
@@ -6945,7 +6949,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -6980,7 +6984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -7015,7 +7019,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
         <v>99</v>
       </c>
@@ -7050,7 +7054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -7085,7 +7089,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -7120,7 +7124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -7155,7 +7159,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
         <v>103</v>
       </c>
@@ -7190,7 +7194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -7225,7 +7229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
         <v>105</v>
       </c>
@@ -7260,7 +7264,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -7295,7 +7299,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -7330,7 +7334,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -7365,7 +7369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -7400,7 +7404,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -7435,7 +7439,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -7470,7 +7474,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -7505,7 +7509,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -7540,7 +7544,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -7575,7 +7579,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -7610,7 +7614,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -7645,7 +7649,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
         <v>117</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -7715,7 +7719,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
         <v>119</v>
       </c>
@@ -7750,7 +7754,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -7785,7 +7789,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -7820,7 +7824,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -7855,7 +7859,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
         <v>123</v>
       </c>
@@ -7890,7 +7894,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -7925,7 +7929,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
         <v>125</v>
       </c>
@@ -7960,7 +7964,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
         <v>126</v>
       </c>
@@ -7995,7 +7999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
         <v>127</v>
       </c>
@@ -8030,7 +8034,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -8065,7 +8069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
         <v>129</v>
       </c>
@@ -8100,7 +8104,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -8135,7 +8139,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
         <v>131</v>
       </c>
@@ -8170,7 +8174,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
         <v>132</v>
       </c>
@@ -8205,7 +8209,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
         <v>133</v>
       </c>
@@ -8240,7 +8244,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
         <v>134</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
         <v>135</v>
       </c>
@@ -8310,7 +8314,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
         <v>136</v>
       </c>
@@ -8345,7 +8349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
         <v>137</v>
       </c>
@@ -8380,7 +8384,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
         <v>138</v>
       </c>
@@ -8415,7 +8419,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
         <v>139</v>
       </c>
@@ -8450,7 +8454,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
         <v>140</v>
       </c>
@@ -8485,7 +8489,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
         <v>141</v>
       </c>
@@ -8520,7 +8524,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
         <v>142</v>
       </c>
@@ -8555,7 +8559,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
         <v>143</v>
       </c>
@@ -8590,7 +8594,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
         <v>144</v>
       </c>
@@ -8625,7 +8629,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
         <v>145</v>
       </c>
@@ -8660,7 +8664,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -8695,7 +8699,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
         <v>147</v>
       </c>
@@ -8730,7 +8734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
         <v>148</v>
       </c>
@@ -8765,7 +8769,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
         <v>149</v>
       </c>
@@ -8800,7 +8804,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
         <v>150</v>
       </c>
@@ -8835,7 +8839,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
         <v>151</v>
       </c>
@@ -8870,7 +8874,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
         <v>152</v>
       </c>
@@ -8905,7 +8909,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
         <v>153</v>
       </c>
@@ -8940,7 +8944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
         <v>154</v>
       </c>
@@ -8975,7 +8979,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
         <v>155</v>
       </c>
@@ -9010,7 +9014,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
         <v>156</v>
       </c>
@@ -9045,7 +9049,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
         <v>157</v>
       </c>
@@ -9080,7 +9084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
         <v>158</v>
       </c>
@@ -9115,7 +9119,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
         <v>159</v>
       </c>
@@ -9150,7 +9154,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
         <v>160</v>
       </c>
@@ -9185,7 +9189,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
         <v>161</v>
       </c>
@@ -9220,7 +9224,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
         <v>162</v>
       </c>
@@ -9255,7 +9259,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
         <v>163</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
         <v>164</v>
       </c>
@@ -9325,7 +9329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
         <v>165</v>
       </c>
@@ -9360,7 +9364,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
         <v>166</v>
       </c>
@@ -9395,7 +9399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
         <v>167</v>
       </c>
@@ -9430,7 +9434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
         <v>168</v>
       </c>
@@ -9465,7 +9469,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
         <v>169</v>
       </c>
@@ -9500,7 +9504,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
         <v>170</v>
       </c>
@@ -9535,7 +9539,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
         <v>171</v>
       </c>
@@ -9570,7 +9574,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
         <v>172</v>
       </c>
@@ -9605,7 +9609,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
         <v>173</v>
       </c>
@@ -9640,7 +9644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
         <v>174</v>
       </c>
@@ -9675,7 +9679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
         <v>175</v>
       </c>
@@ -9710,7 +9714,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
         <v>176</v>
       </c>
@@ -9745,7 +9749,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
         <v>177</v>
       </c>
@@ -9780,7 +9784,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
         <v>178</v>
       </c>
@@ -9815,7 +9819,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
         <v>179</v>
       </c>
@@ -9850,7 +9854,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
         <v>180</v>
       </c>
@@ -9885,7 +9889,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
         <v>181</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
         <v>182</v>
       </c>
@@ -9955,7 +9959,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
         <v>183</v>
       </c>
@@ -9990,7 +9994,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
         <v>184</v>
       </c>
@@ -10025,7 +10029,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
         <v>185</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
         <v>186</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
         <v>187</v>
       </c>
@@ -10130,7 +10134,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
         <v>188</v>
       </c>
@@ -10165,7 +10169,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
         <v>189</v>
       </c>
@@ -10200,7 +10204,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
         <v>190</v>
       </c>
@@ -10235,7 +10239,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
         <v>191</v>
       </c>
@@ -10270,7 +10274,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
         <v>192</v>
       </c>
@@ -10305,7 +10309,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
         <v>193</v>
       </c>
@@ -10340,7 +10344,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
         <v>194</v>
       </c>
@@ -10375,7 +10379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
         <v>195</v>
       </c>
@@ -10410,7 +10414,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
         <v>196</v>
       </c>
@@ -10445,7 +10449,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
         <v>197</v>
       </c>
@@ -10480,7 +10484,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
         <v>198</v>
       </c>
@@ -10515,7 +10519,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
         <v>199</v>
       </c>
@@ -10550,7 +10554,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
         <v>200</v>
       </c>
@@ -10585,7 +10589,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
         <v>201</v>
       </c>
@@ -10620,7 +10624,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
         <v>202</v>
       </c>
@@ -10655,7 +10659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
         <v>203</v>
       </c>
@@ -10690,7 +10694,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
         <v>204</v>
       </c>
@@ -10725,7 +10729,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
         <v>205</v>
       </c>
@@ -10760,7 +10764,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
         <v>206</v>
       </c>
@@ -10795,7 +10799,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
         <v>207</v>
       </c>
@@ -10830,7 +10834,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
         <v>208</v>
       </c>
@@ -10865,7 +10869,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
         <v>209</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
         <v>210</v>
       </c>
@@ -10935,7 +10939,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
         <v>211</v>
       </c>
@@ -10970,7 +10974,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
         <v>212</v>
       </c>
@@ -11005,7 +11009,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
         <v>213</v>
       </c>
@@ -11040,7 +11044,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
         <v>214</v>
       </c>
@@ -11075,7 +11079,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
         <v>215</v>
       </c>
@@ -11110,7 +11114,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
         <v>216</v>
       </c>
@@ -11145,7 +11149,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
         <v>217</v>
       </c>
@@ -11180,7 +11184,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
         <v>218</v>
       </c>
@@ -11215,7 +11219,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
         <v>219</v>
       </c>
@@ -11250,7 +11254,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
         <v>220</v>
       </c>
@@ -11285,7 +11289,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
         <v>221</v>
       </c>
@@ -11320,7 +11324,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
         <v>222</v>
       </c>
@@ -11355,7 +11359,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
         <v>223</v>
       </c>
@@ -11390,7 +11394,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
         <v>224</v>
       </c>
@@ -11425,7 +11429,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
         <v>225</v>
       </c>
@@ -11460,7 +11464,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
         <v>226</v>
       </c>
@@ -11495,7 +11499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
         <v>227</v>
       </c>
@@ -11530,7 +11534,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
         <v>228</v>
       </c>
@@ -11565,7 +11569,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
         <v>229</v>
       </c>
@@ -11600,7 +11604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
         <v>230</v>
       </c>
@@ -11635,7 +11639,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
         <v>231</v>
       </c>
@@ -11670,7 +11674,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
         <v>232</v>
       </c>
@@ -11705,7 +11709,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
         <v>233</v>
       </c>
@@ -11740,7 +11744,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
         <v>234</v>
       </c>
@@ -11775,7 +11779,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
         <v>235</v>
       </c>
@@ -11810,7 +11814,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
         <v>236</v>
       </c>
@@ -11845,7 +11849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
         <v>237</v>
       </c>
@@ -11880,7 +11884,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
         <v>238</v>
       </c>
@@ -11915,7 +11919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
         <v>239</v>
       </c>
@@ -11950,7 +11954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
         <v>240</v>
       </c>
@@ -11985,7 +11989,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
         <v>241</v>
       </c>
@@ -12020,7 +12024,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
         <v>242</v>
       </c>
@@ -12055,7 +12059,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
         <v>243</v>
       </c>
@@ -12090,7 +12094,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
         <v>244</v>
       </c>
@@ -12125,7 +12129,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
         <v>245</v>
       </c>
@@ -12160,7 +12164,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
         <v>246</v>
       </c>
@@ -12195,7 +12199,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
         <v>247</v>
       </c>
@@ -12230,7 +12234,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
         <v>248</v>
       </c>
@@ -12265,7 +12269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
         <v>249</v>
       </c>
@@ -12300,7 +12304,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
         <v>250</v>
       </c>
@@ -12335,7 +12339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
         <v>251</v>
       </c>
@@ -12370,7 +12374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
         <v>252</v>
       </c>
@@ -12405,7 +12409,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
         <v>253</v>
       </c>
@@ -12440,7 +12444,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
         <v>254</v>
       </c>
@@ -12475,7 +12479,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
         <v>255</v>
       </c>
@@ -12510,7 +12514,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
         <v>256</v>
       </c>
@@ -12545,7 +12549,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
         <v>257</v>
       </c>
@@ -12580,7 +12584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
         <v>258</v>
       </c>
@@ -12615,7 +12619,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
         <v>259</v>
       </c>
@@ -12650,7 +12654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
         <v>260</v>
       </c>
@@ -12685,7 +12689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
         <v>261</v>
       </c>
@@ -12720,7 +12724,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
         <v>262</v>
       </c>
@@ -12755,7 +12759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
         <v>263</v>
       </c>
@@ -12790,7 +12794,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
         <v>264</v>
       </c>
@@ -12825,7 +12829,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
         <v>265</v>
       </c>
@@ -12860,7 +12864,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
         <v>266</v>
       </c>
@@ -12895,7 +12899,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
         <v>267</v>
       </c>
@@ -12930,7 +12934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
         <v>268</v>
       </c>
@@ -12965,7 +12969,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
         <v>269</v>
       </c>
@@ -13000,7 +13004,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
         <v>270</v>
       </c>
@@ -13035,7 +13039,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
         <v>271</v>
       </c>
@@ -13070,7 +13074,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
         <v>272</v>
       </c>
@@ -13105,7 +13109,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
         <v>273</v>
       </c>
@@ -13140,7 +13144,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
         <v>274</v>
       </c>
@@ -13175,7 +13179,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
         <v>275</v>
       </c>
@@ -13210,7 +13214,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
         <v>276</v>
       </c>
@@ -13245,7 +13249,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
         <v>277</v>
       </c>
@@ -13280,7 +13284,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
         <v>278</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
         <v>279</v>
       </c>
@@ -13350,7 +13354,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
         <v>280</v>
       </c>
@@ -13385,7 +13389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
         <v>281</v>
       </c>
@@ -13420,7 +13424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
         <v>282</v>
       </c>
@@ -13455,7 +13459,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
         <v>283</v>
       </c>
@@ -13490,7 +13494,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
         <v>284</v>
       </c>
@@ -13525,7 +13529,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
         <v>285</v>
       </c>
@@ -13560,7 +13564,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
         <v>286</v>
       </c>
@@ -13595,7 +13599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
         <v>287</v>
       </c>
@@ -13630,7 +13634,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
         <v>288</v>
       </c>
@@ -13665,7 +13669,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
         <v>289</v>
       </c>
@@ -13700,7 +13704,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
         <v>290</v>
       </c>
@@ -13735,7 +13739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
         <v>291</v>
       </c>
@@ -13770,7 +13774,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
         <v>292</v>
       </c>
@@ -13805,7 +13809,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
         <v>293</v>
       </c>
@@ -13840,7 +13844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
         <v>294</v>
       </c>
@@ -13875,7 +13879,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
         <v>295</v>
       </c>
@@ -13910,7 +13914,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
         <v>296</v>
       </c>
@@ -13945,7 +13949,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
         <v>297</v>
       </c>
@@ -13980,7 +13984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
         <v>298</v>
       </c>
@@ -14015,7 +14019,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
         <v>299</v>
       </c>
@@ -14050,7 +14054,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
         <v>300</v>
       </c>
@@ -14085,7 +14089,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
         <v>301</v>
       </c>
@@ -14120,7 +14124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
         <v>302</v>
       </c>
@@ -14155,7 +14159,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
         <v>303</v>
       </c>
@@ -14190,7 +14194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
         <v>304</v>
       </c>
@@ -14225,7 +14229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
         <v>305</v>
       </c>
@@ -14260,7 +14264,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
         <v>306</v>
       </c>
@@ -14330,7 +14334,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
         <v>308</v>
       </c>
@@ -14365,7 +14369,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
         <v>309</v>
       </c>
@@ -14400,7 +14404,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
         <v>310</v>
       </c>
@@ -14435,7 +14439,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
         <v>311</v>
       </c>
@@ -14470,7 +14474,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
         <v>312</v>
       </c>
@@ -14505,7 +14509,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
         <v>313</v>
       </c>
@@ -14540,7 +14544,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
         <v>314</v>
       </c>
@@ -14575,7 +14579,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
         <v>315</v>
       </c>
@@ -14610,7 +14614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
         <v>316</v>
       </c>
@@ -14645,7 +14649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
         <v>317</v>
       </c>
@@ -14680,7 +14684,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
         <v>318</v>
       </c>
@@ -14715,7 +14719,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
         <v>319</v>
       </c>
@@ -14750,7 +14754,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
         <v>320</v>
       </c>
@@ -14785,7 +14789,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
         <v>321</v>
       </c>
@@ -14820,7 +14824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
         <v>322</v>
       </c>
@@ -14855,7 +14859,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
         <v>323</v>
       </c>
@@ -14890,7 +14894,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
         <v>324</v>
       </c>
@@ -14925,7 +14929,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
         <v>325</v>
       </c>
@@ -14960,7 +14964,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
         <v>326</v>
       </c>
@@ -14995,7 +14999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
         <v>327</v>
       </c>
@@ -15030,7 +15034,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
         <v>328</v>
       </c>
@@ -15065,7 +15069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
         <v>329</v>
       </c>
@@ -15100,7 +15104,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
         <v>330</v>
       </c>
@@ -15135,7 +15139,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
         <v>331</v>
       </c>
@@ -15170,7 +15174,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
         <v>332</v>
       </c>
@@ -15205,7 +15209,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
         <v>333</v>
       </c>
@@ -15240,7 +15244,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
         <v>334</v>
       </c>
@@ -15275,7 +15279,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
         <v>335</v>
       </c>
@@ -15310,7 +15314,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
         <v>336</v>
       </c>
@@ -15345,7 +15349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
         <v>337</v>
       </c>
@@ -15380,7 +15384,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
         <v>338</v>
       </c>
@@ -15415,7 +15419,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
         <v>339</v>
       </c>
@@ -15450,7 +15454,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
         <v>340</v>
       </c>
@@ -15485,7 +15489,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
         <v>341</v>
       </c>
@@ -15520,7 +15524,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
         <v>342</v>
       </c>
@@ -15555,7 +15559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
         <v>343</v>
       </c>
@@ -15590,7 +15594,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
         <v>344</v>
       </c>
@@ -15625,7 +15629,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
         <v>345</v>
       </c>
@@ -15660,7 +15664,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
         <v>346</v>
       </c>
@@ -15695,7 +15699,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
         <v>347</v>
       </c>
@@ -15730,7 +15734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
         <v>348</v>
       </c>
@@ -15765,7 +15769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
         <v>349</v>
       </c>
@@ -15800,7 +15804,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
         <v>350</v>
       </c>
@@ -15835,7 +15839,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
         <v>351</v>
       </c>
@@ -15870,7 +15874,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
         <v>352</v>
       </c>
@@ -15905,7 +15909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
         <v>353</v>
       </c>
@@ -15940,7 +15944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
         <v>354</v>
       </c>
@@ -15975,7 +15979,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
         <v>355</v>
       </c>
@@ -16010,7 +16014,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
         <v>356</v>
       </c>
@@ -16045,7 +16049,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
         <v>357</v>
       </c>
@@ -16080,7 +16084,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
         <v>358</v>
       </c>
@@ -16115,7 +16119,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
         <v>359</v>
       </c>
@@ -16150,7 +16154,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
         <v>360</v>
       </c>
@@ -16185,7 +16189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
         <v>361</v>
       </c>
@@ -16220,7 +16224,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
         <v>362</v>
       </c>
@@ -16255,7 +16259,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
         <v>363</v>
       </c>
@@ -16290,7 +16294,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
         <v>364</v>
       </c>
@@ -16325,7 +16329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
         <v>365</v>
       </c>
@@ -16360,7 +16364,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
         <v>366</v>
       </c>
@@ -16395,7 +16399,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
         <v>367</v>
       </c>
@@ -16430,7 +16434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
         <v>368</v>
       </c>
@@ -16465,7 +16469,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
         <v>369</v>
       </c>
@@ -16500,7 +16504,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
         <v>370</v>
       </c>
@@ -16535,7 +16539,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
         <v>371</v>
       </c>
@@ -16570,7 +16574,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
         <v>372</v>
       </c>
@@ -16605,7 +16609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
         <v>373</v>
       </c>
@@ -16640,7 +16644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
         <v>374</v>
       </c>
@@ -16675,7 +16679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
         <v>375</v>
       </c>
@@ -16710,7 +16714,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
         <v>376</v>
       </c>
@@ -16745,7 +16749,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
         <v>377</v>
       </c>
@@ -16780,7 +16784,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
         <v>378</v>
       </c>
@@ -16815,7 +16819,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
         <v>379</v>
       </c>
@@ -16850,7 +16854,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
         <v>380</v>
       </c>
@@ -16885,7 +16889,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
         <v>381</v>
       </c>
@@ -16920,7 +16924,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
         <v>382</v>
       </c>
@@ -16955,7 +16959,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
         <v>383</v>
       </c>
@@ -16990,7 +16994,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
         <v>384</v>
       </c>
@@ -17025,7 +17029,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
         <v>385</v>
       </c>
@@ -17060,7 +17064,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
         <v>386</v>
       </c>
@@ -17095,7 +17099,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
         <v>387</v>
       </c>
@@ -17130,7 +17134,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
         <v>388</v>
       </c>
@@ -17165,7 +17169,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
         <v>389</v>
       </c>
@@ -17200,7 +17204,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
         <v>390</v>
       </c>
@@ -17235,7 +17239,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
         <v>391</v>
       </c>
@@ -17270,7 +17274,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
         <v>392</v>
       </c>
@@ -17305,7 +17309,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
         <v>393</v>
       </c>
@@ -17340,7 +17344,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
         <v>394</v>
       </c>
@@ -17375,7 +17379,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
         <v>395</v>
       </c>
@@ -17410,7 +17414,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
         <v>396</v>
       </c>
@@ -17445,7 +17449,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
         <v>397</v>
       </c>
@@ -17480,7 +17484,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
         <v>398</v>
       </c>
@@ -17515,7 +17519,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
         <v>399</v>
       </c>
@@ -17550,7 +17554,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
         <v>400</v>
       </c>
@@ -17585,7 +17589,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
         <v>401</v>
       </c>
@@ -17620,7 +17624,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
         <v>402</v>
       </c>
@@ -17655,7 +17659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
         <v>403</v>
       </c>
@@ -17690,7 +17694,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
         <v>404</v>
       </c>
@@ -17725,7 +17729,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
         <v>405</v>
       </c>
@@ -17760,7 +17764,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
         <v>406</v>
       </c>
@@ -17795,7 +17799,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
         <v>407</v>
       </c>
@@ -17830,7 +17834,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
         <v>408</v>
       </c>
@@ -17865,7 +17869,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
         <v>409</v>
       </c>
@@ -17900,7 +17904,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
         <v>410</v>
       </c>
@@ -17935,7 +17939,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
         <v>411</v>
       </c>
@@ -17970,7 +17974,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
         <v>412</v>
       </c>
@@ -18005,7 +18009,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
         <v>413</v>
       </c>
@@ -18040,7 +18044,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
         <v>414</v>
       </c>
@@ -18075,7 +18079,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
         <v>415</v>
       </c>
@@ -18110,7 +18114,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
         <v>416</v>
       </c>
@@ -18145,7 +18149,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
         <v>417</v>
       </c>
@@ -18180,7 +18184,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
         <v>418</v>
       </c>
@@ -18215,7 +18219,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
         <v>419</v>
       </c>
@@ -18250,7 +18254,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
         <v>420</v>
       </c>
@@ -18285,7 +18289,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
         <v>421</v>
       </c>
@@ -18320,7 +18324,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
         <v>422</v>
       </c>
@@ -18355,7 +18359,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
         <v>423</v>
       </c>
@@ -18390,7 +18394,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
         <v>424</v>
       </c>
@@ -18425,7 +18429,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6">
         <v>425</v>
       </c>
@@ -18460,7 +18464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6">
         <v>426</v>
       </c>
@@ -18495,7 +18499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6">
         <v>427</v>
       </c>
@@ -18530,7 +18534,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6">
         <v>428</v>
       </c>
@@ -18565,7 +18569,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6">
         <v>429</v>
       </c>
@@ -18600,7 +18604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6">
         <v>430</v>
       </c>
@@ -18635,7 +18639,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6">
         <v>431</v>
       </c>
@@ -18670,7 +18674,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6">
         <v>432</v>
       </c>
@@ -18705,7 +18709,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="6">
         <v>433</v>
       </c>
@@ -18740,7 +18744,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="6">
         <v>434</v>
       </c>
@@ -18775,7 +18779,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="6">
         <v>435</v>
       </c>
@@ -18810,7 +18814,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="6">
         <v>436</v>
       </c>
@@ -18845,7 +18849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="6">
         <v>437</v>
       </c>
@@ -18880,7 +18884,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="6">
         <v>438</v>
       </c>
@@ -18915,7 +18919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6">
         <v>439</v>
       </c>
@@ -18950,7 +18954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="6">
         <v>440</v>
       </c>
@@ -18985,7 +18989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="6">
         <v>441</v>
       </c>
@@ -19020,7 +19024,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="6">
         <v>442</v>
       </c>
@@ -19055,7 +19059,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="6">
         <v>443</v>
       </c>
@@ -19090,7 +19094,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="6">
         <v>444</v>
       </c>
@@ -19125,7 +19129,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="6">
         <v>445</v>
       </c>
@@ -19160,7 +19164,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6">
         <v>446</v>
       </c>
@@ -19195,7 +19199,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="6">
         <v>447</v>
       </c>
@@ -19230,7 +19234,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="6">
         <v>448</v>
       </c>
@@ -19265,7 +19269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="6">
         <v>449</v>
       </c>
@@ -19300,7 +19304,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6">
         <v>450</v>
       </c>
@@ -19335,7 +19339,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="6">
         <v>451</v>
       </c>
@@ -19370,7 +19374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="6">
         <v>452</v>
       </c>
@@ -19405,7 +19409,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="6">
         <v>453</v>
       </c>
@@ -19440,7 +19444,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="6">
         <v>454</v>
       </c>
@@ -19475,7 +19479,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="6">
         <v>455</v>
       </c>
@@ -19510,7 +19514,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="6">
         <v>456</v>
       </c>
@@ -19545,7 +19549,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="6">
         <v>457</v>
       </c>
@@ -19580,7 +19584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="6">
         <v>458</v>
       </c>
@@ -19615,7 +19619,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="6">
         <v>459</v>
       </c>
@@ -19650,7 +19654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="6">
         <v>460</v>
       </c>
@@ -19685,7 +19689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6">
         <v>461</v>
       </c>
@@ -19720,7 +19724,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="6">
         <v>462</v>
       </c>
@@ -19755,7 +19759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="6">
         <v>463</v>
       </c>
@@ -19790,7 +19794,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="6">
         <v>464</v>
       </c>
@@ -19825,7 +19829,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="6">
         <v>465</v>
       </c>
@@ -19860,7 +19864,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="6">
         <v>466</v>
       </c>
@@ -19895,7 +19899,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="6">
         <v>467</v>
       </c>
@@ -19930,7 +19934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="6">
         <v>468</v>
       </c>
@@ -19965,7 +19969,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6">
         <v>469</v>
       </c>
@@ -20000,7 +20004,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="6">
         <v>470</v>
       </c>
@@ -20035,7 +20039,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="6">
         <v>471</v>
       </c>
@@ -20070,7 +20074,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="6">
         <v>472</v>
       </c>
@@ -20105,7 +20109,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="6">
         <v>473</v>
       </c>
@@ -20140,7 +20144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="6">
         <v>474</v>
       </c>
@@ -20175,7 +20179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="6">
         <v>475</v>
       </c>
@@ -20210,7 +20214,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="6">
         <v>476</v>
       </c>
@@ -20245,7 +20249,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="6">
         <v>477</v>
       </c>
@@ -20280,7 +20284,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="6">
         <v>478</v>
       </c>
@@ -20315,7 +20319,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="6">
         <v>479</v>
       </c>
@@ -20350,7 +20354,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="6">
         <v>480</v>
       </c>
@@ -20385,7 +20389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="6">
         <v>481</v>
       </c>
@@ -20420,7 +20424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="6">
         <v>482</v>
       </c>
@@ -20455,7 +20459,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="6">
         <v>483</v>
       </c>
@@ -20490,7 +20494,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="6">
         <v>484</v>
       </c>
@@ -20525,7 +20529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="6">
         <v>485</v>
       </c>
@@ -20560,7 +20564,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="6">
         <v>486</v>
       </c>
@@ -20595,7 +20599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="6">
         <v>487</v>
       </c>
@@ -20630,7 +20634,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="6">
         <v>488</v>
       </c>
@@ -20665,7 +20669,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="6">
         <v>489</v>
       </c>
@@ -20700,7 +20704,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="6">
         <v>490</v>
       </c>
@@ -20735,7 +20739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="6">
         <v>491</v>
       </c>
@@ -20770,7 +20774,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="6">
         <v>492</v>
       </c>
@@ -20805,7 +20809,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="6">
         <v>493</v>
       </c>
@@ -20840,7 +20844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="6">
         <v>494</v>
       </c>
@@ -20875,7 +20879,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="6">
         <v>495</v>
       </c>
@@ -20910,7 +20914,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="6">
         <v>496</v>
       </c>
@@ -20945,7 +20949,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="6">
         <v>497</v>
       </c>
@@ -20980,7 +20984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="6">
         <v>498</v>
       </c>
@@ -21015,7 +21019,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="6">
         <v>499</v>
       </c>
@@ -21050,7 +21054,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="6">
         <v>500</v>
       </c>
@@ -21085,7 +21089,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="6">
         <v>501</v>
       </c>
@@ -21120,7 +21124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="6">
         <v>502</v>
       </c>
@@ -21155,7 +21159,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="6">
         <v>503</v>
       </c>
@@ -21190,7 +21194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="6">
         <v>504</v>
       </c>
@@ -21225,7 +21229,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="6">
         <v>505</v>
       </c>
@@ -21260,7 +21264,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="6">
         <v>506</v>
       </c>
@@ -21295,7 +21299,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="6">
         <v>507</v>
       </c>
@@ -21330,7 +21334,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="6">
         <v>508</v>
       </c>
@@ -21365,7 +21369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="6">
         <v>509</v>
       </c>
@@ -21400,7 +21404,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="6">
         <v>510</v>
       </c>
@@ -21435,7 +21439,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="6">
         <v>511</v>
       </c>
@@ -21470,7 +21474,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="6">
         <v>512</v>
       </c>
@@ -21505,7 +21509,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="6">
         <v>513</v>
       </c>
@@ -21540,7 +21544,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="6">
         <v>514</v>
       </c>
@@ -21575,7 +21579,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="6">
         <v>515</v>
       </c>
@@ -21610,7 +21614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="6">
         <v>516</v>
       </c>
@@ -21645,7 +21649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="6">
         <v>517</v>
       </c>
@@ -21680,7 +21684,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="6">
         <v>518</v>
       </c>
@@ -21715,7 +21719,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="6">
         <v>519</v>
       </c>
@@ -21750,7 +21754,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="6">
         <v>520</v>
       </c>
@@ -21785,7 +21789,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="6">
         <v>521</v>
       </c>
@@ -21820,7 +21824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="6">
         <v>522</v>
       </c>
@@ -21855,7 +21859,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="6">
         <v>523</v>
       </c>
@@ -21890,7 +21894,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="6">
         <v>524</v>
       </c>
@@ -21925,7 +21929,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="6">
         <v>525</v>
       </c>
@@ -21960,7 +21964,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="6">
         <v>526</v>
       </c>
@@ -21995,7 +21999,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="6">
         <v>527</v>
       </c>
@@ -22030,7 +22034,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="6">
         <v>528</v>
       </c>
@@ -22065,7 +22069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="6">
         <v>529</v>
       </c>
@@ -22100,7 +22104,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="6">
         <v>530</v>
       </c>
@@ -22135,7 +22139,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="6">
         <v>531</v>
       </c>
@@ -22170,7 +22174,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="6">
         <v>532</v>
       </c>
@@ -22205,7 +22209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="6">
         <v>533</v>
       </c>
@@ -22240,7 +22244,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="6">
         <v>534</v>
       </c>
@@ -22275,7 +22279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="6">
         <v>535</v>
       </c>
@@ -22310,7 +22314,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="6">
         <v>536</v>
       </c>
@@ -22345,7 +22349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="6">
         <v>537</v>
       </c>
@@ -22380,7 +22384,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="6">
         <v>538</v>
       </c>
@@ -22415,7 +22419,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="6">
         <v>539</v>
       </c>
@@ -22450,7 +22454,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="6">
         <v>540</v>
       </c>
@@ -22485,7 +22489,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="6">
         <v>541</v>
       </c>
@@ -22520,7 +22524,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="6">
         <v>542</v>
       </c>
@@ -22555,7 +22559,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="6">
         <v>543</v>
       </c>
@@ -22590,7 +22594,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="6">
         <v>544</v>
       </c>
@@ -22625,7 +22629,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="6">
         <v>545</v>
       </c>
@@ -22660,7 +22664,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="6">
         <v>546</v>
       </c>
@@ -22695,7 +22699,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="6">
         <v>547</v>
       </c>
@@ -22730,7 +22734,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="6">
         <v>548</v>
       </c>
@@ -22765,7 +22769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="6">
         <v>549</v>
       </c>
@@ -22800,7 +22804,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="6">
         <v>550</v>
       </c>
@@ -22835,7 +22839,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="6">
         <v>551</v>
       </c>
@@ -22870,7 +22874,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="6">
         <v>552</v>
       </c>
@@ -22905,7 +22909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="6">
         <v>553</v>
       </c>
@@ -22940,7 +22944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="6">
         <v>554</v>
       </c>
@@ -22975,7 +22979,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="6">
         <v>555</v>
       </c>
@@ -23010,7 +23014,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="6">
         <v>556</v>
       </c>
@@ -23045,7 +23049,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="6">
         <v>557</v>
       </c>
@@ -23080,7 +23084,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="6">
         <v>558</v>
       </c>
@@ -23115,7 +23119,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="6">
         <v>559</v>
       </c>
@@ -23150,7 +23154,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="6">
         <v>560</v>
       </c>
@@ -23185,7 +23189,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="6">
         <v>561</v>
       </c>
@@ -23220,7 +23224,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="6">
         <v>562</v>
       </c>
@@ -23255,7 +23259,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="6">
         <v>563</v>
       </c>
@@ -23290,7 +23294,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="6">
         <v>564</v>
       </c>
@@ -23325,7 +23329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="6">
         <v>565</v>
       </c>
@@ -23360,7 +23364,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="6">
         <v>566</v>
       </c>
@@ -23395,7 +23399,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="6">
         <v>567</v>
       </c>
@@ -23430,7 +23434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="6">
         <v>568</v>
       </c>
@@ -23465,7 +23469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="6">
         <v>569</v>
       </c>
@@ -23500,7 +23504,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="6">
         <v>570</v>
       </c>
@@ -23535,7 +23539,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="6">
         <v>571</v>
       </c>
@@ -23570,7 +23574,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="6">
         <v>572</v>
       </c>
@@ -23605,7 +23609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="6">
         <v>573</v>
       </c>
@@ -23640,7 +23644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="6">
         <v>574</v>
       </c>
@@ -23675,7 +23679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="6">
         <v>575</v>
       </c>
@@ -23710,7 +23714,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="6">
         <v>576</v>
       </c>
@@ -23745,7 +23749,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="6">
         <v>577</v>
       </c>
@@ -23781,6 +23785,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B578">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="KAPA OIL REFINERIES LTD"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
